--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>40</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,24 +898,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 107,3%</t>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,7%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,3%</t>
+        <v>55</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,5%</t>
+        <v>41</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,8%</t>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>99</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1825,19 +1825,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,33 +1939,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1975,19 +1975,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2092,22 +2092,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>74</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2125,19 +2125,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,33 +2239,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,33 +2389,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,6%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,33 +2539,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,0%</t>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2694,20 +2694,20 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,2%</t>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2770,8 +2770,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2780,37 +2782,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2835,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+        <v>71</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2878,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2916,47 +2920,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2984,30 +2992,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3024,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3054,7 +3062,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3062,8 +3070,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>1</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3072,37 +3082,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3127,33 +3139,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>77</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3170,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3200,7 +3212,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3208,10 +3220,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3220,39 +3230,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3277,33 +3285,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>83</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3320,12 +3328,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3350,7 +3358,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3358,51 +3366,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3427,33 +3431,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3470,12 +3474,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3500,7 +3504,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3508,10 +3512,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3520,39 +3522,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3577,33 +3577,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>103</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3727,33 +3727,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3877,33 +3877,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4027,33 +4027,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4108,8 +4108,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4118,37 +4120,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4173,33 +4177,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,0%</t>
+        <v>96</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4216,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4246,7 +4250,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4254,47 +4258,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4319,25 +4327,25 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>115</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4345,7 +4353,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4362,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4392,7 +4400,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4400,8 +4408,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>1</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4410,37 +4420,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4465,33 +4477,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>70</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4508,12 +4520,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4538,7 +4550,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4546,10 +4558,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4558,39 +4568,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4615,33 +4623,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>92</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4658,12 +4666,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4688,7 +4696,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4696,51 +4704,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4765,25 +4769,25 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,5%</t>
+        <v>73</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4791,7 +4795,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4808,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4838,7 +4842,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4846,10 +4850,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4858,39 +4860,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 473,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4924,24 +4924,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5074,11 +5074,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>75</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5215,25 +5215,25 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 59,0%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5365,33 +5365,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>78</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5446,8 +5446,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5456,37 +5458,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5511,33 +5515,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5554,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5584,7 +5588,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5592,47 +5596,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5657,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5700,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5730,7 +5738,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5738,47 +5746,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>1</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5803,33 +5815,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,7%</t>
+        <v>39</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5846,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5885,7 +5897,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5919,12 +5931,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5949,33 +5961,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 39,9%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>95</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5992,12 +6004,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6022,7 +6034,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6030,51 +6042,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6099,33 +6107,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>75</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6142,82 +6150,524 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>42</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -739,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,5%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -889,33 +885,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,0%</t>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1039,33 +1035,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1155,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1189,33 +1185,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1305,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1348,24 +1344,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 107,3%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1455,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1492,17 +1488,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,7%</t>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1605,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1639,33 +1635,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▲ 249,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,3%</t>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1755,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1789,33 +1785,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+        <v>131</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1828,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1905,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1939,33 +1935,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,5%</t>
+        <v>99</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1978,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2055,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2089,33 +2085,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,8%</t>
+        <v>84</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2128,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2205,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2239,33 +2235,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>74</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2275,19 +2271,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2355,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2389,33 +2385,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2505,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2539,33 +2535,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,4%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2578,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2655,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2689,33 +2685,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,2%</t>
+        <v>46</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2728,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,14 +2805,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2839,33 +2835,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,6%</t>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2878,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,14 +2955,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2989,33 +2985,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,0%</t>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3032,12 +3028,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,14 +3105,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3142,22 +3138,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3165,7 +3161,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3182,14 +3178,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3212,7 +3208,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3220,8 +3216,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3230,39 +3228,41 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3285,33 +3285,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+        <v>77</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3369,9 +3369,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3401,14 +3401,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3431,33 +3431,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,0%</t>
+        <v>83</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3474,14 +3474,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3513,11 +3513,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3577,25 +3577,25 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,14 +3620,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3658,10 +3658,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3670,41 +3668,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3727,16 +3723,16 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3745,15 +3741,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,14 +3843,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3877,7 +3873,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3899,11 +3895,11 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3916,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3997,14 +3993,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4030,17 +4026,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4070,12 +4066,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4147,14 +4143,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4177,33 +4173,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4220,12 +4216,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4297,14 +4293,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4327,33 +4323,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 64,3%</t>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4370,12 +4366,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4447,14 +4443,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4480,22 +4476,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4503,7 +4499,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4520,14 +4516,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4550,7 +4546,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4558,8 +4554,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4568,39 +4566,41 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4623,33 +4623,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,0%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4707,9 +4707,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4739,14 +4739,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4772,30 +4772,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,0%</t>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4812,14 +4812,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4851,11 +4851,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4885,14 +4885,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4915,33 +4915,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,3%</t>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,14 +4958,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4996,10 +4996,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5008,41 +5006,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5065,33 +5061,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5108,12 +5104,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,14 +5181,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5215,33 +5211,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5254,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,14 +5331,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5365,33 +5361,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>87</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5404,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,14 +5481,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5515,33 +5511,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>78</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5558,12 +5554,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,14 +5631,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5665,33 +5661,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 59,0%</t>
+        <v>76</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5708,12 +5704,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,14 +5781,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5815,33 +5811,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,9%</t>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5858,14 +5854,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5888,7 +5884,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5896,8 +5892,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5906,39 +5904,41 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5961,33 +5961,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6004,12 +6004,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6045,9 +6045,9 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6077,14 +6077,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6107,33 +6107,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,7%</t>
+        <v>95</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6150,14 +6150,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6189,11 +6189,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6223,14 +6223,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6253,33 +6253,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,7%</t>
+        <v>75</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6369,14 +6369,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6399,25 +6399,25 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 39,9%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6442,14 +6442,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6480,10 +6480,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6492,41 +6490,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6549,33 +6545,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>55</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6592,82 +6588,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,0%</t>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>21</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -888,22 +884,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,5%</t>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -911,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -966,51 +962,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1035,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1044,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 55,0%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1078,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1108,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,10 +1108,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1128,39 +1118,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1194,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>40</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1228,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1335,33 +1323,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1378,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1485,7 +1473,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1494,24 +1482,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▲ 107,3%</t>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1528,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1605,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1644,11 +1632,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 68,7%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1678,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1755,12 +1743,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,33 +1773,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 32,3%</t>
+        <v>55</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1828,12 +1816,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1905,12 +1893,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1935,33 +1923,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1978,12 +1966,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2055,12 +2043,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2085,33 +2073,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 13,5%</t>
+        <v>41</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2128,12 +2116,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2205,12 +2193,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2235,33 +2223,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 29,8%</t>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2278,12 +2266,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2355,12 +2343,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2385,33 +2373,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>99</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2421,19 +2409,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2505,12 +2493,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2535,33 +2523,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2571,19 +2559,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2655,12 +2643,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2688,22 +2676,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>74</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2711,7 +2699,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2721,19 +2709,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2805,12 +2793,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2835,33 +2823,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2878,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2955,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2985,33 +2973,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,6%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3028,12 +3016,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3105,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3135,33 +3123,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,0%</t>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3178,12 +3166,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3255,12 +3243,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3290,20 +3278,20 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,2%</t>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3311,7 +3299,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3328,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3358,7 +3346,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3366,8 +3354,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3376,37 +3366,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3431,33 +3423,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+        <v>71</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3474,12 +3466,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3504,7 +3496,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3512,47 +3504,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3580,30 +3576,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3616,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3650,7 +3646,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3658,8 +3654,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3668,37 +3666,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3723,33 +3723,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>77</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3766,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3804,10 +3804,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3816,39 +3814,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3873,33 +3869,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>83</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3916,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3946,7 +3942,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3954,51 +3950,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4023,33 +4015,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4066,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4096,7 +4088,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4104,10 +4096,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4116,39 +4106,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4173,33 +4161,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>103</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4216,12 +4204,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4293,12 +4281,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4323,33 +4311,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4366,12 +4354,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4443,12 +4431,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4473,33 +4461,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4516,12 +4504,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4593,12 +4581,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4623,33 +4611,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4666,12 +4654,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4696,7 +4684,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4704,8 +4692,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4714,37 +4704,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4769,33 +4761,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,0%</t>
+        <v>96</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4812,12 +4804,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4842,7 +4834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4850,47 +4842,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4915,25 +4911,25 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>115</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4941,7 +4937,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4954,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4988,7 +4984,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4996,8 +4992,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5006,37 +5004,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5061,33 +5061,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>70</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5142,10 +5142,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5154,39 +5152,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5211,33 +5207,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>92</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5254,12 +5250,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5284,7 +5280,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5292,51 +5288,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5361,25 +5353,25 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,5%</t>
+        <v>73</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5387,7 +5379,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5404,12 +5396,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5434,7 +5426,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5442,10 +5434,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5454,39 +5444,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5511,7 +5499,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 473,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5520,24 +5508,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5554,12 +5542,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5631,12 +5619,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5670,11 +5658,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>75</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5704,12 +5692,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5781,12 +5769,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5811,25 +5799,25 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 59,0%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5837,7 +5825,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5854,12 +5842,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5931,12 +5919,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5961,33 +5949,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>78</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6004,12 +5992,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6034,7 +6022,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6042,8 +6030,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6052,37 +6042,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6107,33 +6099,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6150,12 +6142,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6180,7 +6172,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6188,47 +6180,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6253,33 +6249,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6296,12 +6292,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6326,7 +6322,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6334,47 +6330,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>1</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6399,33 +6399,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 32,7%</t>
+        <v>39</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6515,12 +6515,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6545,33 +6545,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 39,9%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>95</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6626,51 +6626,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6695,33 +6691,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>75</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6738,82 +6734,524 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 185,7%</t>
+        <v>93</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,2%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -819,9 +819,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 19,0%</t>
+        <v>52</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -957,17 +957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>60</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 37,9%</t>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,51 +1254,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1326,22 +1322,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1349,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1396,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1404,51 +1400,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1473,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1482,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1516,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1546,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1554,10 +1546,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1566,39 +1556,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1626,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1743,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1773,33 +1761,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>29</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1816,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1893,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1923,7 +1911,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1932,24 +1920,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 107,3%</t>
+        <v>31</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1966,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2043,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2076,17 +2064,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 68,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2116,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2193,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2223,33 +2211,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,3%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2266,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2343,12 +2331,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2373,33 +2361,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+        <v>85</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2416,12 +2404,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2493,12 +2481,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2523,33 +2511,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 13,5%</t>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2566,12 +2554,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2643,12 +2631,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2673,33 +2661,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 29,8%</t>
+        <v>131</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2716,12 +2704,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2793,12 +2781,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2823,33 +2811,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>99</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2859,19 +2847,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2943,12 +2931,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2973,33 +2961,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>84</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3009,19 +2997,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3093,12 +3081,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3128,20 +3116,20 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 32,4%</t>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3149,7 +3137,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3159,19 +3147,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3243,12 +3231,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3273,33 +3261,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3316,12 +3304,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3393,12 +3381,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3423,33 +3411,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,6%</t>
+        <v>57</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3466,12 +3454,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3543,12 +3531,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3573,33 +3561,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,0%</t>
+        <v>46</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3616,12 +3604,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3693,12 +3681,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3726,22 +3714,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,2%</t>
+        <v>68</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3749,7 +3737,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3766,12 +3754,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3796,7 +3784,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3804,8 +3792,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3814,37 +3804,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3869,33 +3861,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3912,12 +3904,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3942,7 +3934,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3950,47 +3942,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4018,30 +4014,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 1,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4058,12 +4054,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4088,7 +4084,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4096,8 +4092,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4106,37 +4104,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4161,33 +4161,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>77</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4242,10 +4242,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4254,39 +4252,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4311,33 +4307,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>83</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4354,12 +4350,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4384,7 +4380,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4392,51 +4388,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4461,33 +4453,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4504,12 +4496,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4534,7 +4526,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4542,10 +4534,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4554,39 +4544,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4611,33 +4599,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>103</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4654,12 +4642,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4731,12 +4719,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4761,33 +4749,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4804,12 +4792,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4881,12 +4869,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4911,33 +4899,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4954,12 +4942,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5031,12 +5019,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5061,33 +5049,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5104,12 +5092,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5134,7 +5122,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5142,8 +5130,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5152,37 +5142,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5207,33 +5199,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,0%</t>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5250,12 +5242,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5280,7 +5272,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5288,47 +5280,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5353,25 +5349,25 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,0%</t>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5379,7 +5375,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5396,12 +5392,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5426,7 +5422,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5434,8 +5430,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>1</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5444,37 +5442,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5499,33 +5499,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,3%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5580,10 +5580,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5592,39 +5590,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5649,33 +5645,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5692,12 +5688,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5722,7 +5718,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5730,51 +5726,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5799,25 +5791,25 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5825,7 +5817,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5842,12 +5834,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5872,7 +5864,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5880,10 +5872,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5892,39 +5882,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5949,7 +5937,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 473,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5958,24 +5946,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>82</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5992,12 +5980,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6069,12 +6057,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6102,17 +6090,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6142,12 +6130,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6219,12 +6207,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6249,25 +6237,25 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 59,0%</t>
+        <v>87</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6275,7 +6263,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6292,12 +6280,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6369,12 +6357,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6399,33 +6387,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,9%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6442,12 +6430,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6472,7 +6460,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6480,8 +6468,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6490,37 +6480,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6545,33 +6537,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>76</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6588,12 +6580,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6618,7 +6610,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6626,47 +6618,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6691,33 +6687,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,7%</t>
+        <v>62</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6734,12 +6730,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6764,7 +6760,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6772,47 +6768,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>1</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6837,33 +6837,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6880,12 +6880,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6953,12 +6953,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6983,33 +6983,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 39,9%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7064,51 +7064,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7133,33 +7129,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>75</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7176,82 +7172,524 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,1%</t>
+          <t>▼ 24,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 76,9%</t>
+        <v>93</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,3%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -957,9 +957,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 185,7%</t>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -1122,11 +1122,11 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,2%</t>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1257,9 +1257,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1268,11 +1268,11 @@
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1470,20 +1470,20 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,0%</t>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>42</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1692,10 +1692,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1704,41 +1702,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1761,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,5%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1881,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -1911,33 +1907,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,0%</t>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1954,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2031,14 +2027,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2061,33 +2057,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2181,14 +2177,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2211,33 +2207,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2254,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2331,14 +2327,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2361,7 +2357,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2370,24 +2366,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 107,3%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2404,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2481,14 +2477,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2514,17 +2510,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,7%</t>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2554,12 +2550,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2631,14 +2627,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2661,33 +2657,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 249,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,3%</t>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2704,12 +2700,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2781,14 +2777,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2811,33 +2807,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+        <v>131</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2854,12 +2850,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2931,14 +2927,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2961,33 +2957,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,5%</t>
+        <v>99</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3004,12 +3000,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3081,14 +3077,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3111,33 +3107,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,8%</t>
+        <v>84</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3154,12 +3150,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3231,14 +3227,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3261,33 +3257,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>74</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3297,19 +3293,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3381,14 +3377,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3411,33 +3407,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3454,12 +3450,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3531,14 +3527,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3561,33 +3557,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,4%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3604,12 +3600,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3681,14 +3677,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3711,33 +3707,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,2%</t>
+        <v>46</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3754,12 +3750,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3831,14 +3827,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3861,33 +3857,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,6%</t>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3904,12 +3900,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3981,14 +3977,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4011,33 +4007,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,0%</t>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4054,12 +4050,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4131,14 +4127,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4164,22 +4160,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4187,7 +4183,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4204,14 +4200,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4234,7 +4230,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4242,8 +4238,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4252,39 +4250,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4307,33 +4307,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+        <v>77</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4350,12 +4350,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,9 +4391,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4423,14 +4423,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4453,33 +4453,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,0%</t>
+        <v>83</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4496,14 +4496,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4535,11 +4535,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4569,14 +4569,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4599,25 +4599,25 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4642,14 +4642,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4680,10 +4680,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4692,41 +4690,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4749,16 +4745,16 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4767,15 +4763,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4792,12 +4788,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4869,14 +4865,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4899,7 +4895,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4921,11 +4917,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4942,12 +4938,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5019,14 +5015,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5052,17 +5048,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5092,12 +5088,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5169,14 +5165,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5199,33 +5195,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5242,12 +5238,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5319,14 +5315,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5349,33 +5345,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 64,3%</t>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5392,12 +5388,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5469,14 +5465,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5502,22 +5498,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5525,7 +5521,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5542,14 +5538,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5572,7 +5568,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5580,8 +5576,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5590,39 +5588,41 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5645,33 +5645,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,0%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5729,9 +5729,9 @@
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5761,14 +5761,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5794,30 +5794,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,0%</t>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5834,14 +5834,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5873,11 +5873,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5907,14 +5907,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5937,33 +5937,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,3%</t>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5980,14 +5980,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6018,10 +6018,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6030,41 +6028,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6087,33 +6083,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6130,12 +6126,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6207,14 +6203,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6237,33 +6233,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6280,12 +6276,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6357,14 +6353,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6387,33 +6383,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>87</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6430,12 +6426,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6507,14 +6503,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6537,33 +6533,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>78</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6580,12 +6576,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6657,14 +6653,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6687,33 +6683,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 59,0%</t>
+        <v>76</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6730,12 +6726,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6807,14 +6803,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6837,33 +6833,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,9%</t>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6880,14 +6876,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6910,7 +6906,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6918,8 +6914,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6928,39 +6926,41 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6983,33 +6983,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7067,9 +7067,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7099,14 +7099,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7129,33 +7129,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,7%</t>
+        <v>95</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7172,14 +7172,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7211,11 +7211,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7245,14 +7245,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7275,33 +7275,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,7%</t>
+        <v>75</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -7391,14 +7391,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7421,25 +7421,25 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 39,9%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7464,14 +7464,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7502,10 +7502,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7514,41 +7512,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7571,33 +7567,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>55</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7614,82 +7610,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,7%</t>
+        <v>81</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,1%</t>
+        <v>66</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,22 +884,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 76,9%</t>
+        <v>70</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -965,9 +965,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>93</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,13 +1103,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 185,7%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1268,11 +1268,11 @@
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,2%</t>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 19,0%</t>
+        <v>60</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1547,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>34</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1838,51 +1838,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1910,22 +1906,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,5%</t>
+        <v>42</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1933,7 +1929,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1988,10 +1984,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2000,39 +1994,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2057,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 55,0%</t>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2100,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2177,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,33 +2199,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2327,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2366,16 +2358,16 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>31</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2383,7 +2375,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2400,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2477,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2510,17 +2502,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 107,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2550,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2627,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2657,33 +2649,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 68,7%</t>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2700,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2777,12 +2769,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2807,33 +2799,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,3%</t>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2850,12 +2842,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2927,12 +2919,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2957,33 +2949,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+        <v>41</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3000,12 +2992,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3077,12 +3069,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3107,33 +3099,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 13,5%</t>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3150,12 +3142,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3227,12 +3219,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3266,16 +3258,16 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 29,8%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3283,7 +3275,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3300,12 +3292,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3377,12 +3369,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3412,20 +3404,20 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>84</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3433,7 +3425,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3443,19 +3435,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3527,12 +3519,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3557,33 +3549,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3593,19 +3585,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3677,12 +3669,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3707,33 +3699,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>57</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3750,12 +3742,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3827,12 +3819,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3857,33 +3849,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3900,12 +3892,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3977,12 +3969,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4016,16 +4008,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,6%</t>
+        <v>46</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4033,7 +4025,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4050,12 +4042,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4127,12 +4119,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4160,22 +4152,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,0%</t>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4183,7 +4175,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4200,12 +4192,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4277,12 +4269,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4307,33 +4299,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,2%</t>
+        <v>71</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4350,12 +4342,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4380,7 +4372,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4388,8 +4380,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4398,37 +4392,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4453,33 +4449,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4496,12 +4492,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4526,7 +4522,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4534,47 +4530,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4604,28 +4604,28 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4715,12 +4715,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4745,33 +4745,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>83</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4826,51 +4826,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4898,30 +4894,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4938,12 +4934,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4968,7 +4964,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4976,10 +4972,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4988,39 +4982,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5045,16 +5037,16 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5063,15 +5055,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5088,12 +5080,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5165,12 +5157,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5195,20 +5187,20 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5217,11 +5209,11 @@
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5238,12 +5230,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5315,12 +5307,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5345,33 +5337,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5388,12 +5380,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5465,12 +5457,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5495,33 +5487,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5538,12 +5530,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5615,12 +5607,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5645,33 +5637,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,9%</t>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5688,12 +5680,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5718,7 +5710,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5726,8 +5718,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5736,37 +5730,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5791,7 +5787,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5800,24 +5796,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,0%</t>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5834,12 +5830,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5864,7 +5860,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5872,47 +5868,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5937,25 +5937,25 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,0%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6053,12 +6053,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6083,33 +6083,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,3%</t>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6164,51 +6164,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6233,33 +6229,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6276,12 +6272,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6306,7 +6302,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6314,10 +6310,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6326,39 +6320,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6383,33 +6375,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6426,12 +6418,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6503,12 +6495,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6533,33 +6525,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>75</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6576,12 +6568,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6653,12 +6645,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6683,33 +6675,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6726,12 +6718,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6803,12 +6795,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6833,33 +6825,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▲ 59,0%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6876,12 +6868,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6953,12 +6945,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6983,33 +6975,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>76</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7026,12 +7018,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7056,7 +7048,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7064,8 +7056,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7074,37 +7068,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7129,33 +7125,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7172,12 +7168,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7202,7 +7198,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7210,47 +7206,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7275,33 +7275,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,7%</t>
+        <v>39</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7357,11 +7357,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7421,33 +7421,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7503,11 +7503,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7567,33 +7567,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▼ 39,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>75</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7610,12 +7610,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7648,51 +7648,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7717,33 +7713,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>73</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7760,82 +7756,378 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,47 +670,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,55 +739,59 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +816,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,8 +824,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>2</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -826,37 +836,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,55 +893,59 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,7%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +970,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,47 +978,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1047,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1090,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1120,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,8 +1128,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1118,37 +1140,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1197,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1206,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 76,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1270,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,8 +1278,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1264,37 +1290,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,17 +1350,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1390,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,16 +1420,18 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1410,37 +1440,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1497,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▲ 185,7%</t>
+          <t>▼ 92,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1540,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1560,11 +1592,11 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1613,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1643,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 38,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 86,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1695,7 +1727,7 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1727,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,22 +1792,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 19,0%</t>
+        <v>98</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1815,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1843,7 +1875,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1935,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>110</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1978,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +2017,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2051,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2081,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,9%</t>
+        <v>95</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,7 +2154,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2130,10 +2162,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2142,39 +2172,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,33 +2227,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,5%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2242,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,7 +2300,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,10 +2308,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2292,39 +2318,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,33 +2373,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,0%</t>
+        <v>81</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,12 +2416,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2422,7 +2446,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2430,51 +2454,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2499,33 +2519,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>66</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,12 +2562,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2572,7 +2592,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2580,10 +2600,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2592,39 +2610,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,33 +2665,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>70</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2722,7 +2738,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2730,51 +2746,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2799,33 +2811,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 107,3%</t>
+        <v>93</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2842,12 +2854,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2872,7 +2884,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2880,10 +2892,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2892,39 +2902,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2949,33 +2957,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 68,7%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2992,12 +3000,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3022,7 +3030,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3030,10 +3038,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3042,39 +3048,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3099,33 +3103,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▲ 249,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,3%</t>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3142,12 +3146,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3172,18 +3176,16 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3192,39 +3194,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3252,22 +3252,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+        <v>60</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3292,12 +3292,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3330,10 +3330,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3342,39 +3340,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3399,33 +3395,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 13,5%</t>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3442,12 +3438,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3472,7 +3468,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3480,51 +3476,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3549,33 +3541,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 29,8%</t>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3592,12 +3584,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3622,7 +3614,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3630,51 +3622,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3702,22 +3690,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>42</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3725,7 +3713,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3735,19 +3723,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3772,7 +3760,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3780,10 +3768,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3792,39 +3778,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3849,33 +3833,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+        <v>40</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3885,19 +3869,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3969,12 +3953,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3999,33 +3983,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>29</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4035,19 +4019,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4119,12 +4103,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4149,33 +4133,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,2%</t>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4185,19 +4169,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4269,12 +4253,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4299,33 +4283,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,6%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4335,19 +4319,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4419,12 +4403,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4449,33 +4433,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,0%</t>
+        <v>55</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4485,19 +4469,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4569,12 +4553,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4599,33 +4583,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,2%</t>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4635,19 +4619,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4672,7 +4656,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4680,8 +4664,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4690,37 +4676,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4745,33 +4733,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,6%</t>
+        <v>41</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4781,19 +4769,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4818,7 +4806,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4826,47 +4814,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4891,33 +4883,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4927,19 +4919,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4964,7 +4956,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4972,8 +4964,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4982,37 +4976,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5042,20 +5038,20 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>99</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5063,7 +5059,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5073,19 +5069,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5157,12 +5153,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5187,33 +5183,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5223,19 +5219,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5307,12 +5303,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5337,33 +5333,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>74</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5373,19 +5369,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5457,12 +5453,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5487,33 +5483,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5530,12 +5526,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5607,12 +5603,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5637,33 +5633,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,5%</t>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5680,12 +5676,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5757,12 +5753,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5790,22 +5786,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 64,3%</t>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5813,7 +5809,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5830,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5907,12 +5903,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5937,33 +5933,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>68</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5980,12 +5976,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6010,7 +6006,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6018,8 +6014,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6028,37 +6026,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6083,33 +6083,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,0%</t>
+        <v>71</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6164,47 +6164,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6232,30 +6236,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>57</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6272,12 +6276,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6302,7 +6306,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6310,8 +6314,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>1</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6320,37 +6326,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6375,33 +6383,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,3%</t>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6418,12 +6426,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6448,7 +6456,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6456,10 +6464,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6468,39 +6474,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6525,33 +6529,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>83</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6568,12 +6572,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6598,7 +6602,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6606,51 +6610,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6675,25 +6675,25 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6756,10 +6756,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6768,39 +6766,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6825,33 +6821,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>103</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6868,12 +6864,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6945,12 +6941,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6975,20 +6971,20 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6997,11 +6993,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7018,12 +7014,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7095,12 +7091,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7125,33 +7121,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▲ 59,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7168,12 +7164,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7245,12 +7241,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7275,33 +7271,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7318,12 +7314,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7348,7 +7344,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7356,8 +7352,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7366,37 +7364,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7421,33 +7421,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7502,47 +7502,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7567,33 +7571,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,7%</t>
+        <v>115</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7610,12 +7614,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7640,7 +7644,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7648,47 +7652,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>1</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7713,25 +7721,25 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,6%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7739,7 +7747,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7756,12 +7764,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7795,7 +7803,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7829,12 +7837,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7859,33 +7867,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 39,9%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7902,12 +7910,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7932,7 +7940,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7940,51 +7948,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8009,33 +8013,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>73</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8052,82 +8056,1862 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,3%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,5%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,6%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,6%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 59,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,9%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">

--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,14 +2407,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2445,8 +2445,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2455,37 +2457,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2557,12 +2561,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2598,9 +2602,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2630,12 +2634,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2707,14 +2711,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2746,11 +2750,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2780,12 +2784,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2857,14 +2861,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2887,7 +2891,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2895,10 +2899,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2907,39 +2909,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,14 +3165,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3203,8 +3203,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3213,37 +3215,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3315,14 +3319,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3345,7 +3349,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3353,10 +3357,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3365,39 +3367,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3469,14 +3469,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3507,8 +3507,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3517,37 +3519,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3619,12 +3623,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3660,9 +3664,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3692,12 +3696,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3769,14 +3773,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3808,11 +3812,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3842,12 +3846,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3919,14 +3923,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3949,7 +3953,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3957,10 +3961,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3969,39 +3971,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4227,14 +4227,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4265,8 +4265,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4275,37 +4277,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4377,12 +4381,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4418,9 +4422,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4450,12 +4454,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4527,14 +4531,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4566,11 +4570,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4600,12 +4604,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4677,14 +4681,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4710,17 +4714,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4750,14 +4754,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4780,7 +4784,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4788,8 +4792,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4798,39 +4804,41 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4853,33 +4861,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 86,7%</t>
+          <t>▼ 92,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4896,12 +4904,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4937,9 +4945,9 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4969,14 +4977,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4999,33 +5007,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,9%</t>
+          <t>▼ 86,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5042,14 +5050,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5081,11 +5089,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5115,14 +5123,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5145,33 +5153,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>98</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5188,14 +5196,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5227,11 +5235,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5261,14 +5269,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5291,33 +5299,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5334,14 +5342,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5373,11 +5381,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5407,14 +5415,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5437,7 +5445,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -5446,24 +5454,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5480,14 +5488,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5519,7 +5527,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5553,14 +5561,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5583,33 +5591,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,7%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5626,12 +5634,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5667,9 +5675,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5699,14 +5707,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5729,33 +5737,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+        <v>81</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5772,14 +5780,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5811,11 +5819,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5845,14 +5853,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5875,33 +5883,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,7%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5918,14 +5926,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5957,11 +5965,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5991,14 +5999,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6021,33 +6029,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,1%</t>
+        <v>70</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6064,14 +6072,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6103,11 +6111,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6137,14 +6145,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6167,33 +6175,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 76,9%</t>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6210,14 +6218,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6249,7 +6257,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6283,14 +6291,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6313,33 +6321,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>92</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6356,14 +6364,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6389,9 +6397,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
@@ -6429,14 +6437,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6459,33 +6467,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 185,7%</t>
+        <v>52</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6502,14 +6510,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6532,12 +6540,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
@@ -6554,11 +6562,11 @@
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6575,14 +6583,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6605,33 +6613,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,2%</t>
+        <v>60</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6648,14 +6656,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6678,7 +6686,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6689,9 +6697,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6700,11 +6708,11 @@
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6721,14 +6729,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6751,33 +6759,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,0%</t>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6794,14 +6802,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6833,11 +6841,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6867,14 +6875,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6902,20 +6910,20 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6923,7 +6931,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6940,12 +6948,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6983,7 +6991,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7013,14 +7021,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7043,33 +7051,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,9%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7086,14 +7094,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7116,7 +7124,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7124,10 +7132,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7136,41 +7142,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7193,33 +7197,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,5%</t>
+        <v>40</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7236,12 +7240,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7313,14 +7317,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7343,33 +7347,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7386,12 +7390,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7463,14 +7467,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7493,33 +7497,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>31</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7536,12 +7540,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7613,14 +7617,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7643,33 +7647,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7686,12 +7690,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7763,14 +7767,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7793,7 +7797,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7802,24 +7806,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,3%</t>
+        <v>55</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7836,12 +7840,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7913,14 +7917,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7946,17 +7950,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,7%</t>
+        <v>85</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7986,12 +7990,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8063,14 +8067,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8093,33 +8097,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8136,12 +8140,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8213,14 +8217,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8243,33 +8247,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8286,12 +8290,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8363,14 +8367,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8393,33 +8397,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,5%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8436,12 +8440,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8513,14 +8517,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8543,33 +8547,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,8%</t>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8586,12 +8590,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8663,14 +8667,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8693,33 +8697,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>74</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8729,19 +8733,19 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8813,14 +8817,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8843,33 +8847,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8886,12 +8890,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8963,14 +8967,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8993,33 +8997,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>57</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9036,12 +9040,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9113,14 +9117,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9143,33 +9147,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,2%</t>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9186,12 +9190,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9263,14 +9267,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9293,33 +9297,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,6%</t>
+        <v>68</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9336,12 +9340,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9413,14 +9417,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9443,33 +9447,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,0%</t>
+        <v>71</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9486,12 +9490,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9563,14 +9567,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9596,22 +9600,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,2%</t>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
@@ -9619,7 +9623,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9636,14 +9640,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9666,7 +9670,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9674,8 +9678,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9684,39 +9690,41 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9739,33 +9747,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9782,12 +9790,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9823,9 +9831,9 @@
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9855,14 +9863,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9885,33 +9893,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9928,14 +9936,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9967,11 +9975,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -10001,14 +10009,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10031,25 +10039,25 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
@@ -10057,7 +10065,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10074,14 +10082,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10104,7 +10112,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10112,10 +10120,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10124,41 +10130,39 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10181,16 +10185,16 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10199,15 +10203,15 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10224,12 +10228,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10301,14 +10305,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10331,7 +10335,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10353,11 +10357,11 @@
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10374,12 +10378,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10451,14 +10455,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10484,17 +10488,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10524,12 +10528,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10601,14 +10605,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10631,33 +10635,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10674,12 +10678,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10751,14 +10755,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10781,33 +10785,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>96</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10824,12 +10828,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10901,14 +10905,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10934,22 +10938,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>115</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
@@ -10957,7 +10961,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10974,14 +10978,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11004,7 +11008,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11012,8 +11016,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11022,39 +11028,41 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11077,33 +11085,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,0%</t>
+        <v>70</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11120,12 +11128,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11161,9 +11169,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11193,14 +11201,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11226,30 +11234,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>92</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11266,14 +11274,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11305,11 +11313,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11339,14 +11347,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11369,33 +11377,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11412,14 +11420,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11442,7 +11450,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11450,10 +11458,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11462,41 +11468,39 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11519,33 +11523,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>82</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11562,12 +11566,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11639,14 +11643,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11669,33 +11673,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,5%</t>
+        <v>75</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11712,12 +11716,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11789,14 +11793,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11819,33 +11823,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11862,12 +11866,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11939,14 +11943,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11969,33 +11973,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12012,12 +12016,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12089,14 +12093,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12119,33 +12123,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 59,0%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12162,12 +12166,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12239,14 +12243,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12269,33 +12273,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>62</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12312,14 +12316,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12342,7 +12346,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12350,8 +12354,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>0</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12360,39 +12366,41 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12415,33 +12423,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>39</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12458,12 +12466,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12499,9 +12507,9 @@
       <c r="I161" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12531,14 +12539,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12561,33 +12569,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12604,14 +12612,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12643,11 +12651,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12665,7 +12673,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12677,14 +12685,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12707,33 +12715,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12750,12 +12758,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12793,7 +12801,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12811,7 +12819,7 @@
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
@@ -12823,14 +12831,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12853,25 +12861,25 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,9%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
@@ -12879,7 +12887,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12896,14 +12904,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12926,7 +12934,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12934,10 +12942,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12946,41 +12952,39 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13003,33 +13007,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>55</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13046,82 +13050,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2561,14 +2561,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2599,8 +2599,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2609,37 +2611,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2711,12 +2715,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2752,9 +2756,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2784,12 +2788,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2861,14 +2865,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2900,11 +2904,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2934,12 +2938,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3011,14 +3015,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3049,10 +3053,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3061,39 +3063,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,14 +3319,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3357,8 +3357,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3367,37 +3369,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3469,14 +3473,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3499,7 +3503,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3507,10 +3511,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3519,39 +3521,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3623,14 +3623,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3661,8 +3661,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3671,37 +3673,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3773,12 +3777,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3814,9 +3818,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3846,12 +3850,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3923,14 +3927,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3962,11 +3966,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3996,12 +4000,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4073,14 +4077,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4103,7 +4107,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4111,10 +4115,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4123,39 +4125,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4381,14 +4381,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4419,8 +4419,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4429,37 +4431,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4531,12 +4535,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4572,9 +4576,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4604,12 +4608,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4681,14 +4685,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4720,11 +4724,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4754,12 +4758,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4831,14 +4835,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4864,17 +4868,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4904,14 +4908,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4934,7 +4938,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4942,8 +4946,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4952,39 +4958,41 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5007,33 +5015,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 86,7%</t>
+          <t>▼ 92,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5050,12 +5058,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5091,9 +5099,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5123,14 +5131,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5153,33 +5161,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,9%</t>
+          <t>▼ 86,7%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5196,14 +5204,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5235,11 +5243,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5269,14 +5277,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5299,33 +5307,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>98</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5342,14 +5350,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5381,11 +5389,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5415,14 +5423,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5445,33 +5453,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5488,14 +5496,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5527,11 +5535,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5561,14 +5569,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5591,7 +5599,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -5600,24 +5608,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5634,14 +5642,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5673,7 +5681,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5707,14 +5715,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5737,33 +5745,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,7%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5780,12 +5788,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5821,9 +5829,9 @@
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5853,14 +5861,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5883,33 +5891,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+        <v>81</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5926,14 +5934,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5965,11 +5973,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5999,14 +6007,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6029,33 +6037,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,7%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6072,14 +6080,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6111,11 +6119,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6145,14 +6153,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6175,33 +6183,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,1%</t>
+        <v>70</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6218,14 +6226,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6257,11 +6265,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6291,14 +6299,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6321,33 +6329,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 76,9%</t>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6364,14 +6372,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6403,7 +6411,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6437,14 +6445,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6467,33 +6475,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>92</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6510,14 +6518,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6543,9 +6551,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
@@ -6583,14 +6591,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6613,33 +6621,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 185,7%</t>
+        <v>52</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6656,14 +6664,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6686,12 +6694,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -6708,11 +6716,11 @@
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6729,14 +6737,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6759,33 +6767,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,2%</t>
+        <v>60</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6802,14 +6810,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6832,7 +6840,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6843,9 +6851,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6854,11 +6862,11 @@
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6875,14 +6883,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6905,33 +6913,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,0%</t>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6948,14 +6956,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6987,11 +6995,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7021,14 +7029,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7056,20 +7064,20 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -7077,7 +7085,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7094,12 +7102,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7137,7 +7145,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7167,14 +7175,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7197,33 +7205,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,9%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7240,14 +7248,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7270,7 +7278,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7278,10 +7286,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7290,41 +7296,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7347,33 +7351,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,5%</t>
+        <v>40</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7390,12 +7394,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7467,14 +7471,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7497,33 +7501,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7540,12 +7544,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7617,14 +7621,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7647,33 +7651,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>31</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7690,12 +7694,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7767,14 +7771,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7797,33 +7801,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7840,12 +7844,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7917,14 +7921,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7947,7 +7951,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7956,24 +7960,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,3%</t>
+        <v>55</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7990,12 +7994,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8067,14 +8071,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8100,17 +8104,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,7%</t>
+        <v>85</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8140,12 +8144,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8217,14 +8221,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8247,33 +8251,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8290,12 +8294,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8367,14 +8371,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8397,33 +8401,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8440,12 +8444,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8517,14 +8521,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8547,33 +8551,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,5%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8590,12 +8594,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8667,14 +8671,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8697,33 +8701,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,8%</t>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8740,12 +8744,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8817,14 +8821,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8847,33 +8851,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>74</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8883,19 +8887,19 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8967,14 +8971,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8997,33 +9001,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9040,12 +9044,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9117,14 +9121,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9147,33 +9151,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>57</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9190,12 +9194,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9267,14 +9271,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9297,33 +9301,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,2%</t>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9340,12 +9344,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9417,14 +9421,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9447,33 +9451,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,6%</t>
+        <v>68</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9490,12 +9494,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9567,14 +9571,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9597,33 +9601,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,0%</t>
+        <v>71</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9640,12 +9644,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9717,14 +9721,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9750,22 +9754,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,2%</t>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
@@ -9773,7 +9777,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9790,14 +9794,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9820,7 +9824,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9828,8 +9832,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9838,39 +9844,41 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9893,33 +9901,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9936,12 +9944,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9977,9 +9985,9 @@
       <c r="I127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -10009,14 +10017,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10039,33 +10047,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10082,14 +10090,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10121,11 +10129,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10155,14 +10163,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10185,25 +10193,25 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
@@ -10211,7 +10219,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10228,14 +10236,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10258,7 +10266,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10266,10 +10274,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10278,41 +10284,39 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10335,16 +10339,16 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10353,15 +10357,15 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10378,12 +10382,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10455,14 +10459,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10485,7 +10489,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10507,11 +10511,11 @@
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10528,12 +10532,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10605,14 +10609,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10638,17 +10642,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10678,12 +10682,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10755,14 +10759,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10785,33 +10789,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10828,12 +10832,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10905,14 +10909,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10935,33 +10939,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>96</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10978,12 +10982,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11055,14 +11059,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11088,22 +11092,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>115</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
@@ -11111,7 +11115,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11128,14 +11132,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11158,7 +11162,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11166,8 +11170,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11176,39 +11182,41 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11231,33 +11239,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,0%</t>
+        <v>70</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11274,12 +11282,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11315,9 +11323,9 @@
       <c r="I145" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11347,14 +11355,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11380,30 +11388,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>92</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11420,14 +11428,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11459,11 +11467,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11493,14 +11501,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11523,33 +11531,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11566,14 +11574,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11596,7 +11604,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11604,10 +11612,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I149" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11616,41 +11622,39 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11673,33 +11677,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>82</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11716,12 +11720,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11793,14 +11797,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11823,33 +11827,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,5%</t>
+        <v>75</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11866,12 +11870,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11943,14 +11947,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11973,33 +11977,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12016,12 +12020,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12093,14 +12097,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12123,33 +12127,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12166,12 +12170,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12243,14 +12247,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12273,33 +12277,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▲ 59,0%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12316,12 +12320,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12393,14 +12397,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12423,33 +12427,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>62</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12466,14 +12470,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12496,7 +12500,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12504,8 +12508,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="n">
-        <v>0</v>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12514,39 +12520,41 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12569,33 +12577,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>39</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12612,12 +12620,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12653,9 +12661,9 @@
       <c r="I163" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12685,14 +12693,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12715,33 +12723,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12758,14 +12766,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12797,11 +12805,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12819,7 +12827,7 @@
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
@@ -12831,14 +12839,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12861,33 +12869,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12904,12 +12912,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12947,7 +12955,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12965,7 +12973,7 @@
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
@@ -12977,14 +12985,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13007,25 +13015,25 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,9%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -13033,7 +13041,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13050,14 +13058,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13080,7 +13088,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -13088,10 +13096,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I169" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -13100,41 +13106,39 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13157,33 +13161,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>55</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13200,82 +13204,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2715,14 +2715,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2753,8 +2753,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2763,37 +2765,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2865,12 +2869,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2906,9 +2910,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2938,12 +2942,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3015,14 +3019,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3054,11 +3058,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3088,12 +3092,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,14 +3169,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3195,7 +3199,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3203,10 +3207,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3215,39 +3217,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3473,14 +3473,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3511,8 +3511,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3521,37 +3523,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3623,14 +3627,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3653,7 +3657,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3661,10 +3665,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3673,39 +3675,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3777,14 +3777,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3815,8 +3815,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3825,37 +3827,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3927,12 +3931,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3968,9 +3972,9 @@
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4000,12 +4004,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4077,14 +4081,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4116,11 +4120,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4150,12 +4154,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4227,14 +4231,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4257,7 +4261,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4265,10 +4269,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4277,39 +4279,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4535,14 +4535,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4573,8 +4573,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4583,37 +4585,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,12 +4689,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4726,9 +4730,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4758,12 +4762,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4835,14 +4839,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -4874,11 +4878,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4908,12 +4912,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4985,14 +4989,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5018,17 +5022,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -5058,14 +5062,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5088,7 +5092,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5096,8 +5100,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5106,39 +5112,41 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5161,33 +5169,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 86,7%</t>
+          <t>▼ 92,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5204,12 +5212,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5245,9 +5253,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5277,14 +5285,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5307,33 +5315,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,9%</t>
+          <t>▼ 86,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5350,14 +5358,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5389,11 +5397,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5423,14 +5431,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5453,33 +5461,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>98</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5496,14 +5504,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5535,11 +5543,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5569,14 +5577,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5599,33 +5607,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5642,14 +5650,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5681,11 +5689,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5715,14 +5723,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5745,7 +5753,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -5754,24 +5762,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5788,14 +5796,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5827,7 +5835,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5861,14 +5869,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -5891,33 +5899,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,7%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5934,12 +5942,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5975,9 +5983,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -6007,14 +6015,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6037,33 +6045,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+        <v>81</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6080,14 +6088,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6119,11 +6127,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6153,14 +6161,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6183,33 +6191,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,7%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6226,14 +6234,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6265,11 +6273,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6299,14 +6307,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6329,33 +6337,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,1%</t>
+        <v>70</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6372,14 +6380,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6411,11 +6419,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6445,14 +6453,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6475,33 +6483,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 76,9%</t>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6518,14 +6526,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6557,7 +6565,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6591,14 +6599,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6621,33 +6629,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>92</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6664,14 +6672,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6697,9 +6705,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -6737,14 +6745,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6767,33 +6775,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 185,7%</t>
+        <v>52</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6810,14 +6818,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6840,12 +6848,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
@@ -6862,11 +6870,11 @@
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6883,14 +6891,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6913,33 +6921,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,2%</t>
+        <v>60</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6956,14 +6964,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -6986,7 +6994,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6997,9 +7005,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7008,11 +7016,11 @@
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7029,14 +7037,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7059,33 +7067,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,0%</t>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7102,14 +7110,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7141,11 +7149,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7175,14 +7183,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7210,20 +7218,20 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7231,7 +7239,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7248,12 +7256,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7291,7 +7299,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7321,14 +7329,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7351,33 +7359,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,9%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7394,14 +7402,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7424,7 +7432,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7432,10 +7440,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7444,41 +7450,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7501,33 +7505,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,5%</t>
+        <v>40</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7544,12 +7548,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7621,14 +7625,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7651,33 +7655,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7694,12 +7698,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7771,14 +7775,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7801,33 +7805,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>31</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7844,12 +7848,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7921,14 +7925,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -7951,33 +7955,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,3%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7994,12 +7998,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8071,14 +8075,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8101,7 +8105,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8110,24 +8114,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,3%</t>
+        <v>55</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8144,12 +8148,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8221,14 +8225,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8254,17 +8258,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,7%</t>
+        <v>85</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8294,12 +8298,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8371,14 +8375,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8401,33 +8405,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8444,12 +8448,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8521,14 +8525,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8551,33 +8555,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 552,00</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,9%</t>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8594,12 +8598,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8671,14 +8675,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8701,33 +8705,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,5%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8744,12 +8748,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8821,14 +8825,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -8851,33 +8855,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,8%</t>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8894,12 +8898,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8971,14 +8975,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9001,33 +9005,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>74</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9037,19 +9041,19 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9121,14 +9125,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9151,33 +9155,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 23,9%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9194,12 +9198,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9271,14 +9275,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9301,33 +9305,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>57</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9344,12 +9348,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9421,14 +9425,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9451,33 +9455,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,2%</t>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9494,12 +9498,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9571,14 +9575,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9601,33 +9605,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,6%</t>
+        <v>68</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9644,12 +9648,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9721,14 +9725,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9751,33 +9755,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,0%</t>
+        <v>71</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9794,12 +9798,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9871,14 +9875,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9904,22 +9908,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,2%</t>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
@@ -9927,7 +9931,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9944,14 +9948,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -9974,7 +9978,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9982,8 +9986,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="n">
-        <v>0</v>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9992,39 +9998,41 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10047,33 +10055,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10090,12 +10098,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10131,9 +10139,9 @@
       <c r="I129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10163,14 +10171,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10193,33 +10201,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▼ 1,0%</t>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10236,14 +10244,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10275,11 +10283,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10309,14 +10317,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10339,25 +10347,25 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>102</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
@@ -10365,7 +10373,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10382,14 +10390,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10412,7 +10420,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10420,10 +10428,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10432,41 +10438,39 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10489,16 +10493,16 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10507,15 +10511,15 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10532,12 +10536,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10609,14 +10613,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10639,7 +10643,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10661,11 +10665,11 @@
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10682,12 +10686,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10759,14 +10763,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10792,17 +10796,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10832,12 +10836,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10909,14 +10913,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -10939,33 +10943,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10982,12 +10986,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11059,14 +11063,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11089,33 +11093,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>96</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11132,12 +11136,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11209,14 +11213,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11242,22 +11246,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>115</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
@@ -11265,7 +11269,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11282,14 +11286,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11312,7 +11316,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11320,8 +11324,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11330,39 +11336,41 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11385,33 +11393,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,0%</t>
+        <v>70</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11428,12 +11436,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11469,9 +11477,9 @@
       <c r="I147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11501,14 +11509,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11534,30 +11542,30 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>92</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11574,14 +11582,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11613,11 +11621,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11647,14 +11655,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11677,33 +11685,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11720,14 +11728,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11750,7 +11758,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11758,10 +11766,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11770,41 +11776,39 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11827,33 +11831,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,8%</t>
+        <v>82</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11870,12 +11874,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11947,14 +11951,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -11977,33 +11981,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,5%</t>
+        <v>75</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12020,12 +12024,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12097,14 +12101,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12127,33 +12131,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,6%</t>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12170,12 +12174,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12247,14 +12251,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12277,33 +12281,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12320,12 +12324,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12397,14 +12401,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12427,33 +12431,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 59,0%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12470,12 +12474,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12547,14 +12551,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12577,33 +12581,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>62</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12620,14 +12624,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12650,7 +12654,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12658,8 +12662,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="n">
-        <v>0</v>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12668,39 +12674,41 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12723,33 +12731,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>39</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12766,12 +12774,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12807,9 +12815,9 @@
       <c r="I165" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12839,14 +12847,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12869,33 +12877,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12912,14 +12920,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -12951,11 +12959,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12973,7 +12981,7 @@
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
@@ -12985,14 +12993,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13015,33 +13023,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13058,12 +13066,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13101,7 +13109,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13119,7 +13127,7 @@
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
@@ -13131,14 +13139,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13161,25 +13169,25 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 148,00</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,9%</t>
+          <t>▼ 33,6%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
@@ -13187,7 +13195,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13204,14 +13212,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13234,7 +13242,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13242,10 +13250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I171" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -13254,41 +13260,39 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-025-PT</t>
@@ -13311,33 +13315,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>55</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13354,82 +13358,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-025-PT-CARRINHO-PRATELEIRA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2907,8 +2907,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2917,37 +2919,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3019,12 +3023,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3049,7 +3053,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3057,47 +3061,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3169,12 +3177,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3199,7 +3207,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3207,8 +3215,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>1</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3217,37 +3227,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,12 +3331,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3396,12 +3408,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3473,12 +3485,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3503,7 +3515,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3511,10 +3523,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3523,39 +3533,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3627,12 +3635,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3668,9 +3676,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3700,12 +3708,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3777,12 +3785,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3807,7 +3815,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3815,10 +3823,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3827,39 +3833,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3931,12 +3935,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3961,7 +3965,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3969,8 +3973,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3979,37 +3985,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4081,12 +4089,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4111,7 +4119,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4119,47 +4127,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4231,12 +4243,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4270,7 +4282,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4304,12 +4316,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4381,12 +4393,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4458,12 +4470,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4535,12 +4547,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4565,7 +4577,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4573,10 +4585,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4585,39 +4595,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4689,12 +4697,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4730,9 +4738,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4762,12 +4770,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4839,12 +4847,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4878,11 +4886,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4912,12 +4920,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4989,12 +4997,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5019,7 +5027,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5027,47 +5035,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5139,12 +5151,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5169,55 +5181,59 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,3%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5242,7 +5258,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5250,8 +5266,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5260,37 +5278,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5315,33 +5335,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 86,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5358,12 +5378,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5388,7 +5408,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5396,47 +5416,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5461,33 +5485,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5504,12 +5528,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5534,7 +5558,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5542,8 +5566,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>1</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5552,37 +5578,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5607,33 +5635,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,8%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5650,12 +5678,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5680,7 +5708,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5688,47 +5716,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5753,33 +5785,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 92,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5796,12 +5828,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5835,7 +5867,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5869,12 +5901,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5902,22 +5934,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 86,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5925,7 +5957,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5942,12 +5974,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5983,9 +6015,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -6015,12 +6047,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6045,33 +6077,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,7%</t>
+        <v>98</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6088,12 +6120,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6127,11 +6159,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6161,12 +6193,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6191,33 +6223,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,7%</t>
+        <v>110</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6234,12 +6266,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6273,11 +6305,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6307,12 +6339,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6337,33 +6369,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,7%</t>
+        <v>95</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6380,12 +6412,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6419,11 +6451,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6453,12 +6485,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6483,33 +6515,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,1%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6526,12 +6558,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6565,7 +6597,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6599,12 +6631,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6629,33 +6661,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 76,9%</t>
+          <t>▲ 22,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6672,12 +6704,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6713,9 +6745,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6745,12 +6777,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6775,33 +6807,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,3%</t>
+          <t>▼ 5,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6818,12 +6850,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6851,13 +6883,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6891,12 +6923,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6921,33 +6953,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 185,7%</t>
+        <v>70</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6964,12 +6996,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6994,7 +7026,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -7005,9 +7037,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7016,11 +7048,11 @@
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7037,12 +7069,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7067,33 +7099,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,2%</t>
+        <v>93</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,1%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7110,12 +7142,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7149,11 +7181,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7183,12 +7215,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7213,33 +7245,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,0%</t>
+        <v>92</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
           <t>2,9%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7256,12 +7288,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7295,11 +7327,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7329,12 +7361,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7359,33 +7391,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,0%</t>
+        <v>52</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7402,12 +7434,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7435,13 +7467,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7475,12 +7507,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7505,33 +7537,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,9%</t>
+          <t>▲ 185,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7548,12 +7580,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7578,7 +7610,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7586,10 +7618,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7598,39 +7628,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7655,33 +7683,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,5%</t>
+          <t>▼ 38,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7698,12 +7726,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7728,7 +7756,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7736,51 +7764,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7805,33 +7829,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7848,12 +7872,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7878,7 +7902,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7886,51 +7910,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7955,33 +7975,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>42</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7998,12 +8018,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8028,7 +8048,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8036,10 +8056,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -8048,39 +8066,37 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8105,33 +8121,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,3%</t>
+        <v>40</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,9%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8148,12 +8164,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8225,12 +8241,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8255,33 +8271,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,3%</t>
+        <v>29</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,5%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8298,12 +8314,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8375,12 +8391,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8405,33 +8421,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,7%</t>
+        <v>31</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8448,12 +8464,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8525,12 +8541,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8555,33 +8571,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 552,00</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 249,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8598,12 +8614,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8675,12 +8691,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8708,22 +8724,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,9%</t>
+        <v>55</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,3%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
@@ -8731,7 +8747,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8748,12 +8764,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8825,12 +8841,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8855,33 +8871,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,5%</t>
+          <t>▲ 107,3%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8898,12 +8914,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8975,12 +8991,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9005,33 +9021,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,7%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9048,12 +9064,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9125,12 +9141,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9155,33 +9171,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 552,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 249,4%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>131</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9191,19 +9207,19 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9275,12 +9291,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9305,33 +9321,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,9%</t>
+          <t>▲ 17,9%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9341,19 +9357,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9425,12 +9441,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9455,33 +9471,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,4%</t>
+        <v>84</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,5%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9491,19 +9507,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9575,12 +9591,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9605,33 +9621,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,2%</t>
+        <v>74</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,8%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9641,19 +9657,19 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9725,12 +9741,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9755,33 +9771,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,6%</t>
+        <v>57</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9798,12 +9814,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9875,12 +9891,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9905,33 +9921,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,0%</t>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,9%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9948,12 +9964,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10025,12 +10041,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10055,33 +10071,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,2%</t>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10098,12 +10114,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10128,7 +10144,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10136,8 +10152,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10146,37 +10164,39 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10201,33 +10221,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,6%</t>
+          <t>▼ 4,2%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10244,12 +10264,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10274,7 +10294,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10282,47 +10302,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10347,25 +10371,25 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 1,0%</t>
+        <v>71</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,6%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
@@ -10373,7 +10397,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10390,12 +10414,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10420,7 +10444,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10428,8 +10452,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="n">
-        <v>1</v>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10438,37 +10464,39 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10493,33 +10521,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>57</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10536,12 +10564,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10613,12 +10641,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10646,22 +10674,22 @@
           <t>R$ 237,00</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>77</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,2%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
@@ -10669,7 +10697,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10686,12 +10714,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10716,7 +10744,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10724,10 +10752,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10736,39 +10762,37 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10793,33 +10817,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>83</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10836,12 +10860,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10866,7 +10890,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10874,51 +10898,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10943,33 +10963,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 1,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10986,12 +11006,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11016,7 +11036,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11024,10 +11044,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11036,39 +11054,37 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11093,33 +11109,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,5%</t>
+        <v>103</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11136,12 +11152,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11213,12 +11229,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11243,33 +11259,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 64,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11286,12 +11302,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11363,12 +11379,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11393,33 +11409,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11436,12 +11452,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11466,7 +11482,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11474,8 +11490,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="n">
-        <v>0</v>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11484,37 +11502,39 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11539,33 +11559,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11582,12 +11602,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11612,7 +11632,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11620,47 +11640,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11685,33 +11709,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,0%</t>
+          <t>▼ 16,5%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11728,12 +11752,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11758,7 +11782,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11766,8 +11790,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>1</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11776,37 +11802,39 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11831,33 +11859,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,3%</t>
+          <t>▲ 64,3%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11874,12 +11902,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11951,12 +11979,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11981,33 +12009,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,8%</t>
+          <t>▼ 23,9%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12024,12 +12052,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12054,7 +12082,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12062,10 +12090,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -12074,39 +12100,37 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12131,33 +12155,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,5%</t>
+          <t>▲ 26,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12174,12 +12198,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12204,7 +12228,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12212,51 +12236,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12281,33 +12301,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,6%</t>
+        <v>73</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12324,12 +12344,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12354,7 +12374,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12362,10 +12382,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12374,39 +12392,37 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12431,33 +12447,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,6%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12474,12 +12490,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12551,12 +12567,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12581,33 +12597,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 59,0%</t>
+        <v>75</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,8%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12624,12 +12640,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12701,12 +12717,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12731,33 +12747,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,9%</t>
+        <v>87</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,5%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12774,12 +12790,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12804,7 +12820,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12812,8 +12828,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="n">
-        <v>0</v>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
@@ -12822,37 +12840,39 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12877,7 +12897,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12886,24 +12906,24 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▲ 2,6%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12920,12 +12940,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12950,7 +12970,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12958,47 +12978,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13032,11 +13056,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 22,6%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13066,12 +13090,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13096,7 +13120,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -13104,47 +13128,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="n">
-        <v>1</v>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13178,16 +13206,16 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 59,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
@@ -13195,7 +13223,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13212,12 +13240,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13242,7 +13270,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13250,8 +13278,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="2" t="n">
-        <v>1</v>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -13260,37 +13290,39 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13320,28 +13352,28 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,9%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▼ 58,9%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13358,12 +13390,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13388,7 +13420,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -13396,10 +13428,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I173" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -13408,39 +13438,37 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13465,7 +13493,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 371,00</t>
+          <t>R$ 297,00</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -13474,16 +13502,16 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>95</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
@@ -13491,7 +13519,7 @@
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13508,82 +13536,670 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,6%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,9%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4502495809</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-PT</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho Prateleira Preto</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4502432861</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 371,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-PT</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho Prateleira Preto</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4502495809</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>